--- a/config/_TableConfig/Game.Global-全局单例.xlsx
+++ b/config/_TableConfig/Game.Global-全局单例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18960" windowHeight="10390"/>
+    <workbookView windowWidth="22210" windowHeight="11510"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>##column##var</t>
   </si>
@@ -39,36 +39,6 @@
   </si>
   <si>
     <t>描述</t>
-  </si>
-  <si>
-    <t>battle_map_length</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>战役地图边长</t>
-  </si>
-  <si>
-    <t>battle_down_round_count_max</t>
-  </si>
-  <si>
-    <t>战斗倒地回合计数上限</t>
-  </si>
-  <si>
-    <t>artifact_field</t>
-  </si>
-  <si>
-    <t>奇物栏位数量上限</t>
-  </si>
-  <si>
-    <t>default_abilities</t>
-  </si>
-  <si>
-    <t>(array#sep=|), int</t>
-  </si>
-  <si>
-    <t>默认能力</t>
   </si>
 </sst>
 </file>
@@ -1045,60 +1015,28 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="2">
-        <v>25</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="2"/>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2">
-        <v>3</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="2"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" s="2">
-        <v>3</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="2"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="2">
-        <v>50001</v>
-      </c>
+      <c r="A6" s="3"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/config/_TableConfig/Game.Global-全局单例.xlsx
+++ b/config/_TableConfig/Game.Global-全局单例.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22210" windowHeight="11510"/>
+    <workbookView windowHeight="15120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>##column##var</t>
   </si>
@@ -39,6 +39,15 @@
   </si>
   <si>
     <t>描述</t>
+  </si>
+  <si>
+    <t>max_level</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>最高等级</t>
   </si>
 </sst>
 </file>
@@ -55,7 +64,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -69,7 +78,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -77,14 +86,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -92,7 +101,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -100,7 +109,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -108,7 +117,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -116,7 +125,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -124,14 +133,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -139,7 +148,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -147,7 +156,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -155,14 +164,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -170,42 +179,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -669,55 +678,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -987,7 +996,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="30.6363636363636" customWidth="1"/>
     <col min="2" max="2" width="16.8181818181818" customWidth="1"/>
@@ -1015,10 +1024,18 @@
       <c r="D2" s="2"/>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="2"/>
+      <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1"/>
